--- a/data/trans_dic/P21D_6_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,56</t>
+          <t>1,35; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,51</t>
+          <t>0,79; 2,4</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,3</t>
+          <t>0,14; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,14</t>
+          <t>0,7; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,37</t>
+          <t>0,48; 1,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,07</t>
+          <t>0,08; 1,14</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,05</t>
+          <t>0,2; 1,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,78</t>
+          <t>0,85; 1,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,3</t>
+          <t>0,6; 1,25</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5431</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4024; 11980</t>
+          <t>4532; 12885</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4970; 14248</t>
+          <t>4486; 13597</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1807; 14541</t>
+          <t>1515; 14458</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6942; 20015</t>
+          <t>6562; 20182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10511; 28049</t>
+          <t>9906; 26837</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5693</t>
+          <t>0; 6147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2721</t>
+          <t>0; 2593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>522; 6661</t>
+          <t>518; 7111</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3337; 17330</t>
+          <t>3375; 16869</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13534; 28248</t>
+          <t>13431; 28812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20117; 42106</t>
+          <t>19371; 40582</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_6_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_6_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,29; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,4</t>
+          <t>0,77; 2,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,2; 1,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,15</t>
+          <t>0,75; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,31</t>
+          <t>0,62; 1,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,14</t>
+          <t>0,07; 0,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,02</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,82</t>
+          <t>0,84; 1,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,25</t>
+          <t>0,64; 1,25</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8818</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5083</t>
+          <t>0; 5079</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4532; 12885</t>
+          <t>4686; 13241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4486; 13597</t>
+          <t>4708; 14715</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17838</t>
+          <t>18502</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1515; 14458</t>
+          <t>1884; 14103</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6562; 20182</t>
+          <t>7395; 19923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9906; 26837</t>
+          <t>12025; 28840</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2240</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6147</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2593</t>
+          <t>0; 2672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>518; 7111</t>
+          <t>506; 6816</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3375; 16869</t>
+          <t>3880; 17153</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13431; 28812</t>
+          <t>14170; 28554</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19371; 40582</t>
+          <t>20776; 40502</t>
         </is>
       </c>
     </row>
